--- a/Feuilles/Les mains.xlsx
+++ b/Feuilles/Les mains.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF263895-76C2-5748-B29A-6EC3FBDA3287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FA125E-5422-1C4D-928D-30AD51D19C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40040" yWindow="2080" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>MES</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>THEME 4</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -472,13 +475,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,8 +494,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -506,7 +512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -517,7 +523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -528,7 +534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -539,7 +545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -550,7 +556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -561,7 +567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -572,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -583,7 +589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -597,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -608,7 +614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -619,7 +625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -630,7 +636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -644,7 +650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -655,7 +661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Les mains.xlsx
+++ b/Feuilles/Les mains.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FA125E-5422-1C4D-928D-30AD51D19C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8894478E-A905-704A-BE3F-F84E90920B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40040" yWindow="2080" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="1860" yWindow="3180" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -891,7 +891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -948,8 +948,11 @@
       <c r="D40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -960,7 +963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -971,7 +974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -982,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -993,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1004,7 +1007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1038,6 +1041,9 @@
       </c>
       <c r="D48" t="s">
         <v>12</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -1223,7 +1229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1236,8 +1242,11 @@
       <c r="D65" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1248,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1259,7 +1268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1270,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1281,7 +1290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1292,7 +1301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1303,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1314,7 +1323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1327,8 +1336,11 @@
       <c r="D73" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1339,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1350,7 +1362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1361,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1372,7 +1384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1383,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1394,7 +1406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1405,7 +1417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1418,8 +1430,11 @@
       <c r="D81" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1430,7 +1445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1441,7 +1456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1452,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1463,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1474,7 +1489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1485,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1499,7 +1514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1510,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1521,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1532,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1543,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1554,7 +1569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1565,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1576,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
